--- a/registration_forms/034_virtual_game_night_registration_form--registration_forms.xlsx
+++ b/registration_forms/034_virtual_game_night_registration_form--registration_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -905,12 +905,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>game_system_version</t>
+          <t>game_system_version_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Game System Version</t>
+          <t>Game System Version 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -928,12 +928,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>game_name</t>
+          <t>game_name_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Game Name</t>
+          <t>Game Name 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -951,12 +951,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>player_name</t>
+          <t>player_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Player Name</t>
+          <t>Player Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>game_master</t>
+          <t>game_master_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Game Master</t>
+          <t>Game Master 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -997,12 +997,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>game_type</t>
+          <t>game_type_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Game Type</t>
+          <t>Game Type 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>players</t>
+          <t>players_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Players</t>
+          <t>Players 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>platform_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Platform 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>game_system_experience</t>
+          <t>game_system_experience_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Game System Experience</t>
+          <t>Game System Experience 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
